--- a/results/val/binary_AD_results.xlsx
+++ b/results/val/binary_AD_results.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,70 +455,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -531,54 +496,33 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.75</v>
+        <v>0.68769</v>
       </c>
       <c r="C2" t="n">
-        <v>0.758</v>
+        <v>0.63</v>
       </c>
       <c r="D2" t="n">
-        <v>0.743</v>
+        <v>0.75701</v>
       </c>
       <c r="E2" t="n">
-        <v>0.862</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.862</v>
+        <v>0.875</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.65385</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.33333</v>
       </c>
       <c r="J2" t="n">
-        <v>0.875</v>
+        <v>0.4</v>
       </c>
       <c r="K2" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.728</v>
-      </c>
-      <c r="R2" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -589,54 +533,33 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.727</v>
+        <v>0.70483</v>
       </c>
       <c r="C3" t="n">
-        <v>0.737</v>
+        <v>0.67425</v>
       </c>
       <c r="D3" t="n">
-        <v>0.718</v>
+        <v>0.73832</v>
       </c>
       <c r="E3" t="n">
-        <v>0.849</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.849</v>
+        <v>0.875</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.61538</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>0.33333</v>
       </c>
       <c r="J3" t="n">
-        <v>0.875</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="R3" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -647,54 +570,33 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.755</v>
+        <v>0.7202</v>
       </c>
       <c r="C4" t="n">
-        <v>0.779</v>
+        <v>0.68681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.733</v>
+        <v>0.75701</v>
       </c>
       <c r="E4" t="n">
-        <v>0.876</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.876</v>
+        <v>0.875</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.69231</v>
       </c>
       <c r="I4" t="n">
-        <v>0.824</v>
+        <v>0.22222</v>
       </c>
       <c r="J4" t="n">
-        <v>0.875</v>
+        <v>0.4</v>
       </c>
       <c r="K4" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.737</v>
-      </c>
-      <c r="R4" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -705,54 +607,33 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.736</v>
+        <v>0.7110300000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.766</v>
+        <v>0.68569</v>
       </c>
       <c r="D5" t="n">
-        <v>0.708</v>
+        <v>0.73832</v>
       </c>
       <c r="E5" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.867</v>
+        <v>0.875</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.65385</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.22222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.875</v>
+        <v>0.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="R5" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -767,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,70 +674,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -869,55 +715,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.713</v>
+        <v>0.65544</v>
       </c>
       <c r="C2" t="n">
-        <v>0.758</v>
+        <v>0.63</v>
       </c>
       <c r="D2" t="n">
-        <v>0.673</v>
+        <v>0.68301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.847</v>
+        <v>0.96544</v>
       </c>
       <c r="F2" t="n">
-        <v>0.958</v>
+        <v>0.97487</v>
       </c>
       <c r="G2" t="n">
-        <v>0.853</v>
+        <v>0.69572</v>
       </c>
       <c r="H2" t="n">
-        <v>0.975</v>
+        <v>0.6057900000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.726</v>
+        <v>0.33333</v>
       </c>
       <c r="J2" t="n">
-        <v>0.696</v>
+        <v>0.31061</v>
       </c>
       <c r="K2" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.544</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.527</v>
+        <v>0.52721</v>
       </c>
     </row>
     <row r="3">
@@ -927,55 +752,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.67037</v>
       </c>
       <c r="C3" t="n">
-        <v>0.737</v>
+        <v>0.67425</v>
       </c>
       <c r="D3" t="n">
-        <v>0.653</v>
+        <v>0.66652</v>
       </c>
       <c r="E3" t="n">
-        <v>0.832</v>
+        <v>0.96282</v>
       </c>
       <c r="F3" t="n">
-        <v>0.955</v>
+        <v>0.96261</v>
       </c>
       <c r="G3" t="n">
-        <v>0.835</v>
+        <v>0.69762</v>
       </c>
       <c r="H3" t="n">
-        <v>0.963</v>
+        <v>0.5603</v>
       </c>
       <c r="I3" t="n">
-        <v>0.717</v>
+        <v>0.33333</v>
       </c>
       <c r="J3" t="n">
-        <v>0.698</v>
+        <v>0.29318</v>
       </c>
       <c r="K3" t="n">
-        <v>0.522</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.439</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.5</v>
+        <v>0.49963</v>
       </c>
     </row>
     <row r="4">
@@ -985,55 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.701</v>
+        <v>0.67432</v>
       </c>
       <c r="C4" t="n">
-        <v>0.779</v>
+        <v>0.68681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.637</v>
+        <v>0.66228</v>
       </c>
       <c r="E4" t="n">
-        <v>0.854</v>
+        <v>0.94758</v>
       </c>
       <c r="F4" t="n">
-        <v>0.944</v>
+        <v>0.96466</v>
       </c>
       <c r="G4" t="n">
-        <v>0.862</v>
+        <v>0.68984</v>
       </c>
       <c r="H4" t="n">
-        <v>0.965</v>
+        <v>0.64439</v>
       </c>
       <c r="I4" t="n">
-        <v>0.732</v>
+        <v>0.19444</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.31061</v>
       </c>
       <c r="K4" t="n">
-        <v>0.659</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.572</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.398</v>
+        <v>0.39839</v>
       </c>
     </row>
     <row r="5">
@@ -1043,55 +826,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6662</v>
       </c>
       <c r="C5" t="n">
-        <v>0.766</v>
+        <v>0.68569</v>
       </c>
       <c r="D5" t="n">
-        <v>0.62</v>
+        <v>0.64779</v>
       </c>
       <c r="E5" t="n">
-        <v>0.844</v>
+        <v>0.94548</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.95751</v>
       </c>
       <c r="G5" t="n">
-        <v>0.851</v>
+        <v>0.69462</v>
       </c>
       <c r="H5" t="n">
-        <v>0.958</v>
+        <v>0.5989</v>
       </c>
       <c r="I5" t="n">
-        <v>0.728</v>
+        <v>0.22222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.695</v>
+        <v>0.27652</v>
       </c>
       <c r="K5" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.374</v>
+        <v>0.37414</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,70 +893,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -1207,55 +934,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.657</v>
+        <v>0.61299</v>
       </c>
       <c r="C2" t="n">
-        <v>0.758</v>
+        <v>0.63</v>
       </c>
       <c r="D2" t="n">
-        <v>0.58</v>
+        <v>0.59688</v>
       </c>
       <c r="E2" t="n">
-        <v>0.827</v>
+        <v>0.92544</v>
       </c>
       <c r="F2" t="n">
-        <v>0.91</v>
+        <v>0.82551</v>
       </c>
       <c r="G2" t="n">
-        <v>0.79</v>
+        <v>0.48254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.826</v>
+        <v>0.52656</v>
       </c>
       <c r="I2" t="n">
-        <v>0.59</v>
+        <v>0.30556</v>
       </c>
       <c r="J2" t="n">
-        <v>0.483</v>
+        <v>0.25272</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.446</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.281</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.456</v>
+        <v>0.45615</v>
       </c>
     </row>
     <row r="3">
@@ -1265,55 +971,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.633</v>
+        <v>0.6208399999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.737</v>
+        <v>0.67425</v>
       </c>
       <c r="D3" t="n">
-        <v>0.554</v>
+        <v>0.57526</v>
       </c>
       <c r="E3" t="n">
-        <v>0.806</v>
+        <v>0.90845</v>
       </c>
       <c r="F3" t="n">
-        <v>0.889</v>
+        <v>0.78983</v>
       </c>
       <c r="G3" t="n">
-        <v>0.763</v>
+        <v>0.48121</v>
       </c>
       <c r="H3" t="n">
-        <v>0.79</v>
+        <v>0.48843</v>
       </c>
       <c r="I3" t="n">
-        <v>0.582</v>
+        <v>0.29167</v>
       </c>
       <c r="J3" t="n">
-        <v>0.481</v>
+        <v>0.23699</v>
       </c>
       <c r="K3" t="n">
-        <v>0.477</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.429</v>
+        <v>0.4286</v>
       </c>
     </row>
     <row r="4">
@@ -1323,55 +1008,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.66</v>
+        <v>0.63768</v>
       </c>
       <c r="C4" t="n">
-        <v>0.779</v>
+        <v>0.68681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.572</v>
+        <v>0.59511</v>
       </c>
       <c r="E4" t="n">
-        <v>0.831</v>
+        <v>0.90028</v>
       </c>
       <c r="F4" t="n">
-        <v>0.889</v>
+        <v>0.91473</v>
       </c>
       <c r="G4" t="n">
-        <v>0.841</v>
+        <v>0.56347</v>
       </c>
       <c r="H4" t="n">
-        <v>0.915</v>
+        <v>0.57607</v>
       </c>
       <c r="I4" t="n">
-        <v>0.654</v>
+        <v>0.15</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.26981</v>
       </c>
       <c r="K4" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.446</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.312</v>
+        <v>0.31239</v>
       </c>
     </row>
     <row r="5">
@@ -1381,55 +1045,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.644</v>
+        <v>0.62866</v>
       </c>
       <c r="C5" t="n">
-        <v>0.766</v>
+        <v>0.68569</v>
       </c>
       <c r="D5" t="n">
-        <v>0.555</v>
+        <v>0.58039</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.87848</v>
       </c>
       <c r="F5" t="n">
-        <v>0.865</v>
+        <v>0.88391</v>
       </c>
       <c r="G5" t="n">
-        <v>0.821</v>
+        <v>0.57201</v>
       </c>
       <c r="H5" t="n">
-        <v>0.884</v>
+        <v>0.53721</v>
       </c>
       <c r="I5" t="n">
-        <v>0.655</v>
+        <v>0.22222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.572</v>
+        <v>0.2379</v>
       </c>
       <c r="K5" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.294</v>
+        <v>0.29404</v>
       </c>
     </row>
   </sheetData>
@@ -1443,7 +1086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1469,70 +1112,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -1545,55 +1153,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.534</v>
+        <v>0.53301</v>
       </c>
       <c r="C2" t="n">
-        <v>0.709</v>
+        <v>0.60221</v>
       </c>
       <c r="D2" t="n">
-        <v>0.428</v>
+        <v>0.47808</v>
       </c>
       <c r="E2" t="n">
-        <v>0.781</v>
+        <v>0.864</v>
       </c>
       <c r="F2" t="n">
-        <v>0.869</v>
+        <v>0.38444</v>
       </c>
       <c r="G2" t="n">
-        <v>0.499</v>
+        <v>0.20111</v>
       </c>
       <c r="H2" t="n">
-        <v>0.384</v>
+        <v>0.44258</v>
       </c>
       <c r="I2" t="n">
-        <v>0.313</v>
+        <v>0.22222</v>
       </c>
       <c r="J2" t="n">
-        <v>0.201</v>
+        <v>0.21212</v>
       </c>
       <c r="K2" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.456</v>
+        <v>0.45615</v>
       </c>
     </row>
     <row r="3">
@@ -1603,55 +1190,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.484</v>
+        <v>0.53109</v>
       </c>
       <c r="C3" t="n">
-        <v>0.677</v>
+        <v>0.63633</v>
       </c>
       <c r="D3" t="n">
-        <v>0.377</v>
+        <v>0.45573</v>
       </c>
       <c r="E3" t="n">
-        <v>0.76</v>
+        <v>0.88014</v>
       </c>
       <c r="F3" t="n">
-        <v>0.866</v>
+        <v>0.22963</v>
       </c>
       <c r="G3" t="n">
-        <v>0.343</v>
+        <v>0.19887</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>0.40406</v>
       </c>
       <c r="I3" t="n">
-        <v>0.307</v>
+        <v>0.22222</v>
       </c>
       <c r="J3" t="n">
-        <v>0.199</v>
+        <v>0.20478</v>
       </c>
       <c r="K3" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.39</v>
+        <v>0.38959</v>
       </c>
     </row>
     <row r="4">
@@ -1661,55 +1227,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.589</v>
+        <v>0.58031</v>
       </c>
       <c r="C4" t="n">
-        <v>0.721</v>
+        <v>0.6460399999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.498</v>
+        <v>0.52672</v>
       </c>
       <c r="E4" t="n">
-        <v>0.78</v>
+        <v>0.83888</v>
       </c>
       <c r="F4" t="n">
-        <v>0.849</v>
+        <v>0.79225</v>
       </c>
       <c r="G4" t="n">
-        <v>0.755</v>
+        <v>0.38861</v>
       </c>
       <c r="H4" t="n">
-        <v>0.792</v>
+        <v>0.55796</v>
       </c>
       <c r="I4" t="n">
-        <v>0.505</v>
+        <v>0.11111</v>
       </c>
       <c r="J4" t="n">
-        <v>0.389</v>
+        <v>0.26981</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.206</v>
+        <v>0.20633</v>
       </c>
     </row>
     <row r="5">
@@ -1719,55 +1264,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.585</v>
+        <v>0.58464</v>
       </c>
       <c r="C5" t="n">
-        <v>0.715</v>
+        <v>0.64656</v>
       </c>
       <c r="D5" t="n">
-        <v>0.495</v>
+        <v>0.53355</v>
       </c>
       <c r="E5" t="n">
-        <v>0.773</v>
+        <v>0.85061</v>
       </c>
       <c r="F5" t="n">
-        <v>0.842</v>
+        <v>0.76336</v>
       </c>
       <c r="G5" t="n">
-        <v>0.738</v>
+        <v>0.48156</v>
       </c>
       <c r="H5" t="n">
-        <v>0.763</v>
+        <v>0.51945</v>
       </c>
       <c r="I5" t="n">
-        <v>0.575</v>
+        <v>0.22222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.482</v>
+        <v>0.20478</v>
       </c>
       <c r="K5" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.182</v>
+        <v>0.18199</v>
       </c>
     </row>
   </sheetData>
@@ -1781,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1807,70 +1331,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T1 F1</t>
+          <t>T1 Recall</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T1 Recall</t>
+          <t>T2 Recall</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T2 F1</t>
+          <t>T3 Recall</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>T2 Recall</t>
+          <t>T4 Recall</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>T3 F1</t>
+          <t>T5 Recall</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>T3 Recall</t>
+          <t>T6 Recall</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T4 F1</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4 Recall</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>T5 F1</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>T5 Recall</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>T6 F1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>T6 Recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>T7 F1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T7 Recall</t>
         </is>
@@ -1883,55 +1372,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.699</v>
+        <v>0.64761</v>
       </c>
       <c r="C2" t="n">
-        <v>0.753</v>
+        <v>0.62722</v>
       </c>
       <c r="D2" t="n">
-        <v>0.658</v>
+        <v>0.67489</v>
       </c>
       <c r="E2" t="n">
-        <v>0.842</v>
+        <v>0.96112</v>
       </c>
       <c r="F2" t="n">
-        <v>0.956</v>
+        <v>0.89601</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.6753400000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.896</v>
+        <v>0.59285</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.31667</v>
       </c>
       <c r="J2" t="n">
-        <v>0.675</v>
+        <v>0.32494</v>
       </c>
       <c r="K2" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.575</v>
+        <v>0.57501</v>
       </c>
     </row>
     <row r="3">
@@ -1941,55 +1409,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.674</v>
+        <v>0.66032</v>
       </c>
       <c r="C3" t="n">
-        <v>0.731</v>
+        <v>0.6704599999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.632</v>
+        <v>0.65591</v>
       </c>
       <c r="E3" t="n">
-        <v>0.826</v>
+        <v>0.95855</v>
       </c>
       <c r="F3" t="n">
-        <v>0.951</v>
+        <v>0.86971</v>
       </c>
       <c r="G3" t="n">
-        <v>0.777</v>
+        <v>0.67541</v>
       </c>
       <c r="H3" t="n">
-        <v>0.87</v>
+        <v>0.5523400000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.31389</v>
       </c>
       <c r="J3" t="n">
-        <v>0.675</v>
+        <v>0.31583</v>
       </c>
       <c r="K3" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.601</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.515</v>
+        <v>0.51457</v>
       </c>
     </row>
     <row r="4">
@@ -1999,55 +1446,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.703</v>
+        <v>0.67594</v>
       </c>
       <c r="C4" t="n">
-        <v>0.773</v>
+        <v>0.6827299999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.648</v>
+        <v>0.67318</v>
       </c>
       <c r="E4" t="n">
-        <v>0.85</v>
+        <v>0.94822</v>
       </c>
       <c r="F4" t="n">
-        <v>0.946</v>
+        <v>0.95157</v>
       </c>
       <c r="G4" t="n">
-        <v>0.853</v>
+        <v>0.70851</v>
       </c>
       <c r="H4" t="n">
-        <v>0.952</v>
+        <v>0.64125</v>
       </c>
       <c r="I4" t="n">
-        <v>0.731</v>
+        <v>0.18833</v>
       </c>
       <c r="J4" t="n">
-        <v>0.709</v>
+        <v>0.33413</v>
       </c>
       <c r="K4" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.304</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.483</v>
+        <v>0.48263</v>
       </c>
     </row>
     <row r="5">
@@ -2057,55 +1483,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.66847</v>
       </c>
       <c r="C5" t="n">
-        <v>0.761</v>
+        <v>0.6817800000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.63</v>
+        <v>0.6591</v>
       </c>
       <c r="E5" t="n">
-        <v>0.84</v>
+        <v>0.9444</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.94037</v>
       </c>
       <c r="G5" t="n">
-        <v>0.84</v>
+        <v>0.72094</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.60059</v>
       </c>
       <c r="I5" t="n">
-        <v>0.734</v>
+        <v>0.22222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.721</v>
+        <v>0.31101</v>
       </c>
       <c r="K5" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.434</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.534</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.429</v>
+        <v>0.42925</v>
       </c>
     </row>
   </sheetData>
